--- a/bombeio.xlsx
+++ b/bombeio.xlsx
@@ -1,67 +1,133 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygor.silva\Downloads\Simulador v2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15501260-CC78-46F4-8EC8-C3D16ECF887C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bombeio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bombeio" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>Royal FIC — Base de Bombeio Petrobras (edite apenas as colunas C e D)</t>
+  </si>
+  <si>
+    <t>Não altere a coluna A (código do produto usado pelo simulador). Preço já em R$/L.</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Preco_RS_L</t>
+  </si>
+  <si>
+    <t>Atualizado_em</t>
+  </si>
+  <si>
+    <t>gasolina</t>
+  </si>
+  <si>
+    <t>Gasolina A</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>s10</t>
+  </si>
+  <si>
+    <t>Diesel S10</t>
+  </si>
+  <si>
+    <t>s500</t>
+  </si>
+  <si>
+    <t>Diesel S500</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1A3E6F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A3E6F"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF5A7399"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="005A7399"/>
-      <sz val="9"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A3E6F"/>
-        <bgColor rgb="001A3E6F"/>
+        <fgColor rgb="FF1A3E6F"/>
+        <bgColor rgb="FF1A3E6F"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,105 +141,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C8D6E8"/>
+        <color rgb="FFC8D6E8"/>
       </left>
       <right style="thin">
-        <color rgb="00C8D6E8"/>
+        <color rgb="FFC8D6E8"/>
       </right>
       <top style="thin">
-        <color rgb="00C8D6E8"/>
+        <color rgb="FFC8D6E8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C8D6E8"/>
+        <color rgb="FFC8D6E8"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -461,114 +470,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Royal FIC — Base de Bombeio Petrobras (edite apenas as colunas C e D)</t>
-        </is>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Não altere a coluna A (código do produto usado pelo simulador). Preço já em R$/L.</t>
-        </is>
-      </c>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Preco_RS_L</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Atualizado_em</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>gasolina</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Gasolina A</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5.756199999999998</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>s10</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Diesel S10</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4.9213999999999993</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>s500</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Diesel S500</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.8532000000000002</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/bombeio.xlsx
+++ b/bombeio.xlsx
@@ -5,40 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygor.silva\Downloads\Simulador v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Permanente\Comissao de Preco\Ygor\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15501260-CC78-46F4-8EC8-C3D16ECF887C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9E1F89-CBFA-4EB0-A9C3-1380197F9EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bombeio" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
-  <si>
-    <t>Royal FIC — Base de Bombeio Petrobras (edite apenas as colunas C e D)</t>
-  </si>
-  <si>
-    <t>Não altere a coluna A (código do produto usado pelo simulador). Preço já em R$/L.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+  <si>
+    <t>Royal FIC — Base de Bombeio Petrobras (edite apenas as colunas D e E)</t>
+  </si>
+  <si>
+    <t>Não altere as colunas A, B e C (códigos usados pelo simulador). Preço já em R$/L.</t>
   </si>
   <si>
     <t>Produto</t>
@@ -47,6 +34,9 @@
     <t>Nome</t>
   </si>
   <si>
+    <t>Filial</t>
+  </si>
+  <si>
     <t>Preco_RS_L</t>
   </si>
   <si>
@@ -59,7 +49,10 @@
     <t>Gasolina A</t>
   </si>
   <si>
-    <t>2026-07-27</t>
+    <t>paulinia</t>
+  </si>
+  <si>
+    <t>araucaria</t>
   </si>
   <si>
     <t>s10</t>
@@ -94,27 +87,23 @@
       <sz val="11"/>
       <color rgb="FF1A3E6F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF5A7399"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -165,10 +154,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,32 +460,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -509,53 +501,116 @@
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.7561999999999998</v>
+      </c>
+      <c r="E4" s="7">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
-        <v>5.756199999999998</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
-        <v>4.9213999999999993</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D5" s="3">
+        <v>5.7163000000000004</v>
+      </c>
+      <c r="E5" s="7">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.9214000000000002</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4.8925999999999998</v>
+      </c>
+      <c r="E7" s="7">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3">
         <v>4.8532000000000002</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
+      <c r="E8" s="7">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4.8287000000000004</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46231</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
